--- a/Exportacion_Ictiologica/informacion_ictiologica.xlsx
+++ b/Exportacion_Ictiologica/informacion_ictiologica.xlsx
@@ -12,6 +12,7 @@
     <sheet name="Mediciones" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Evidencias Ocurrencias" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Evidencias Salidas" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Darwin_Core" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2353,4 +2354,779 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>eventID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>eventDate</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eventTime</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>decimalLatitude</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>decimalLongitude</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>samplingProtocol</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>samplingEffort</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>scientificName</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>individualCount</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>organismMeasurementValue_Length</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>organismMeasurementValue_Weight</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>recordedBy</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>occurrenceID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>23:08:00</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>4.4323</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.221813</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Anzuelo</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>79623e83-79ec-4429-8894-5c10b7993d82</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>14:54:00</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>4.730601</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-74.068658</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Atarraya</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v>2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>c4e195f9-0b8b-4e5c-b5e5-ab4acbcc8d4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>14:45:00</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>4.730471</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-74.06873</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Red de arrastre</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>f2dacd60-c201-47bb-bffd-fe00671a3243</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13:04:00</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>4.730642</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-74.068662</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Atarraya</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>88</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="n">
+        <v>88</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>09055c3b-e051-4bdf-800b-40831fe3c2dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>12:56:00</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>4.730587</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-74.068652</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Red de arrastre</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>999</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="n">
+        <v>999</v>
+      </c>
+      <c r="K6" t="n">
+        <v>99</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>a2278f09-b928-4144-bcd5-a6a94fe43e3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>15:20:00</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4.730472</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-74.068754</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Red de arrastre</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>99</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v>99</v>
+      </c>
+      <c r="K7" t="n">
+        <v>99</v>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>8dccd380-a45d-4589-baaa-43f1bfcd7bef</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14:50:35</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>10.391</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-75.479</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa6</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:50:35</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>10.391</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-75.479</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa7</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>14:50:35</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>10.391</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-75.479</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa8</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>14:50:35</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.391</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-75.479</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa1</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>14:50:35</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.391</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-75.479</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa2</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa5</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14:50:35</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>4.711</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-74.07210000000001</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa5</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:50:35</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3fa85f64-5717-4562-b3fc-2c963f66afa5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:55:00</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>4.730564</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-74.068675</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Red de arrastre</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Astyanax fasciatus</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>d594d6cf-317c-4512-8e88-1bf9d12f03ae</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>